--- a/uploads/IDEAS_PRODESIGN.xlsx
+++ b/uploads/IDEAS_PRODESIGN.xlsx
@@ -10237,14 +10237,14 @@
         <v>132</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <f>E9</f>
         <v>132</v>
       </c>
       <c r="F69">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="G69">
         <f>E69/H69</f>

--- a/uploads/IDEAS_PRODESIGN.xlsx
+++ b/uploads/IDEAS_PRODESIGN.xlsx
@@ -9742,7 +9742,7 @@
         <v>600</v>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E43">
         <f>IFERROR(C43/D43,0)</f>
@@ -10159,14 +10159,14 @@
         <v>50</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66">
         <f>E8</f>
         <v>50</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G66">
         <f>E66/H66</f>
@@ -10211,14 +10211,14 @@
         <v>600</v>
       </c>
       <c r="D68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E68">
         <f>E43</f>
         <v>60</v>
       </c>
       <c r="F68">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="G68">
         <f>E68/H68</f>
@@ -10237,14 +10237,14 @@
         <v>132</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69">
         <f>E9</f>
         <v>132</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="G69">
         <f>E69/H69</f>
@@ -10369,14 +10369,14 @@
         <v>90</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <f>CONSOLIDADO!E50</f>
         <v>90</v>
       </c>
       <c r="F74">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G74">
         <f>E74/H74</f>

--- a/uploads/IDEAS_PRODESIGN.xlsx
+++ b/uploads/IDEAS_PRODESIGN.xlsx
@@ -9742,7 +9742,7 @@
         <v>600</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E43">
         <f>IFERROR(C43/D43,0)</f>
@@ -10159,14 +10159,14 @@
         <v>50</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66">
         <f>E8</f>
         <v>50</v>
       </c>
       <c r="F66">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G66">
         <f>E66/H66</f>
@@ -10211,14 +10211,14 @@
         <v>600</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E68">
         <f>E43</f>
         <v>60</v>
       </c>
       <c r="F68">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="G68">
         <f>E68/H68</f>
@@ -10369,14 +10369,14 @@
         <v>90</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74">
         <f>CONSOLIDADO!E50</f>
         <v>90</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G74">
         <f>E74/H74</f>
